--- a/Assets/Resources/Data/Excel/RoomData.xlsx
+++ b/Assets/Resources/Data/Excel/RoomData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\grunge\Assets\Resources\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3552C275-40C7-4002-A14B-C48DD498890E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BEF0EA1-F51D-4890-ACF0-0319AC0402FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{08EE65EB-B8BE-4193-A833-A0B4BB250BB6}"/>
+    <workbookView minimized="1" xWindow="680" yWindow="680" windowWidth="19200" windowHeight="10350" xr2:uid="{08EE65EB-B8BE-4193-A833-A0B4BB250BB6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,13 +25,91 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+  <si>
+    <t>itemID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>RoomData 룸에서 필요한 데이터들, 가져야만 하는 특수 룸 관련 데이터는 여기서 관리하기.</t>
+    <t>roomID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Room_1013</t>
+  </si>
+  <si>
+    <t>Room_1012</t>
+  </si>
+  <si>
+    <t>Room_1011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Room_1010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Room_1009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Room_1008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Room_1007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Room_1006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Room_1005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Room_1004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Room_1003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Room_1002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Room_1001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Room_10_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Room_10_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Room_10_3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Room_10_4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Room_10_5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>isItem</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -396,15 +474,273 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8E08F06-E2EF-43EC-89EA-01CA7AFEC175}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2">
         <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>22001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>23002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" t="b">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>22020</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" t="b">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/Data/Excel/RoomData.xlsx
+++ b/Assets/Resources/Data/Excel/RoomData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26501"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\grunge\Assets\Resources\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BEF0EA1-F51D-4890-ACF0-0319AC0402FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE1B6D35-3195-4151-BB94-AAAD63CF2DA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="680" yWindow="680" windowWidth="19200" windowHeight="10350" xr2:uid="{08EE65EB-B8BE-4193-A833-A0B4BB250BB6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{08EE65EB-B8BE-4193-A833-A0B4BB250BB6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
